--- a/data/trans_dic/IP19C04-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP19C04-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que en su última visita al dentista fue por extracción de algún diente o muela</t>
+          <t>Menores que en su última visita al dentista fue por extracción de algún diente o muela (tasa de respuesta: 99,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,39</t>
+          <t>0,0; 52,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,1</t>
+          <t>0,0; 31,56</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 7,57</t>
+          <t>0,85; 7,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,49; 16,12</t>
+          <t>4,02; 15,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 9,38</t>
+          <t>0,96; 10,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,85; 12,0</t>
+          <t>2,76; 11,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,69; 9,62</t>
+          <t>1,69; 9,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,25; 11,27</t>
+          <t>2,61; 11,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 9,37</t>
+          <t>0,92; 9,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 9,97</t>
+          <t>0,81; 10,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,68; 6,23</t>
+          <t>1,69; 6,45</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,26; 11,01</t>
+          <t>3,88; 11,34</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,81; 7,79</t>
+          <t>1,71; 7,45</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,38; 8,81</t>
+          <t>2,27; 8,64</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,99; 9,15</t>
+          <t>1,92; 9,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,7; 9,08</t>
+          <t>2,73; 9,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,7; 13,96</t>
+          <t>6,13; 14,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,61; 11,92</t>
+          <t>3,93; 11,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,32; 14,92</t>
+          <t>5,27; 15,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,66; 9,61</t>
+          <t>2,7; 9,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,71; 8,98</t>
+          <t>2,79; 9,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,45; 6,67</t>
+          <t>1,55; 6,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,82; 10,94</t>
+          <t>4,58; 10,52</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,36; 7,98</t>
+          <t>3,44; 8,21</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,03; 9,99</t>
+          <t>5,17; 10,38</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,97; 7,54</t>
+          <t>3,22; 7,62</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,12; 12,22</t>
+          <t>5,24; 12,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,33; 9,76</t>
+          <t>3,06; 9,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,15</t>
+          <t>0,43; 3,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,22; 6,44</t>
+          <t>1,17; 6,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,25; 10,56</t>
+          <t>4,58; 10,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,28; 10,0</t>
+          <t>3,29; 9,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,99; 5,16</t>
+          <t>0,98; 5,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 5,56</t>
+          <t>1,21; 5,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,68; 10,18</t>
+          <t>5,66; 10,4</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,01; 8,42</t>
+          <t>3,93; 8,55</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,7</t>
+          <t>0,96; 3,75</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,85</t>
+          <t>1,41; 4,87</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,11; 8,19</t>
+          <t>4,02; 8,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,5; 8,81</t>
+          <t>4,48; 8,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,59; 7,5</t>
+          <t>3,6; 7,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,15; 7,17</t>
+          <t>2,89; 7,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,24; 9,5</t>
+          <t>5,28; 9,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,98; 7,9</t>
+          <t>4,14; 7,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,4; 5,99</t>
+          <t>2,45; 5,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 5,03</t>
+          <t>2,04; 4,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,12; 8,06</t>
+          <t>5,13; 8,25</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,6; 7,69</t>
+          <t>4,65; 7,64</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,41; 6,05</t>
+          <t>3,47; 6,02</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,8; 5,22</t>
+          <t>2,88; 5,21</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en su última visita al dentista fue por extracción de algún diente o muela (tasa de respuesta: 99,51%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2799</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3508</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2273</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6807</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2839</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4022</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>3454</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>5320</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>3196</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2751</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>5727</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>12127</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>6035</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>6773</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>720; 6104</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>3126; 12403</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>662; 7092</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1824; 7838</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1359; 7529</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2407; 10197</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>754; 7772</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>621; 8050</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>2788; 10623</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>6581; 19251</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2575; 11235</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>3246; 12385</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>4559</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6808</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>13887</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>8671</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>9932</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>7181</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>7796</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>5727</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>14490</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>13989</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>21683</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>14398</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1905; 9135</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3418; 11994</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9130; 21560</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>4796; 14369</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>5571; 15948</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3571; 11916</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>4165; 13848</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2549; 11297</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>9394; 21566</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>8847; 21116</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>15420; 30955</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>9218; 21842</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>13688</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>8605</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5686</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>12234</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>8478</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3453</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>6424</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>25921</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>17083</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5907</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>12109</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>8574; 20349</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>4522; 13753</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>618; 5588</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2308; 12757</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>7962; 18507</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>4638; 13975</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1331; 7600</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>2879; 12233</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>19097; 35072</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>11353; 24732</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>2701; 10537</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>6135; 21163</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>20519</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>22220</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>19181</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>18379</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>25619</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>20978</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>14445</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>15609</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>46138</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>43199</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>33626</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>33988</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>14119; 28552</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>15861; 31414</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>13070; 26731</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>11319; 27500</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>19093; 35073</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>15142; 29179</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>9018; 21743</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>9892; 23604</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>36529; 58819</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>33459; 55034</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>25371; 44038</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>25192; 45601</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP19C04-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP19C04-Edad-trans_dic.xlsx
@@ -752,7 +752,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,66</t>
+          <t>0,0; 59,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,56</t>
+          <t>0,0; 30,05</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 7,24</t>
+          <t>0,84; 8,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,02; 15,96</t>
+          <t>4,18; 15,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 10,33</t>
+          <t>1,56; 10,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,76; 11,84</t>
+          <t>2,51; 11,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,69; 9,36</t>
+          <t>1,69; 9,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,61; 11,08</t>
+          <t>2,54; 11,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 9,46</t>
+          <t>0,91; 9,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 10,44</t>
+          <t>0,86; 9,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,69; 6,45</t>
+          <t>1,73; 6,18</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,88; 11,34</t>
+          <t>4,3; 11,36</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,71; 7,45</t>
+          <t>1,89; 7,36</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,27; 8,64</t>
+          <t>2,42; 8,34</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,92; 9,21</t>
+          <t>1,89; 9,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,73; 9,59</t>
+          <t>2,84; 9,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,13; 14,48</t>
+          <t>6,16; 14,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,93; 11,79</t>
+          <t>3,82; 11,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,27; 15,09</t>
+          <t>5,49; 14,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,7; 9,02</t>
+          <t>2,66; 9,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,79; 9,27</t>
+          <t>2,78; 8,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 6,86</t>
+          <t>1,48; 6,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,58; 10,52</t>
+          <t>4,54; 10,56</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,44; 8,21</t>
+          <t>3,44; 8,06</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,17; 10,38</t>
+          <t>5,15; 10,19</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,22; 7,62</t>
+          <t>3,17; 7,6</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,24; 12,45</t>
+          <t>5,32; 12,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,06; 9,3</t>
+          <t>3,23; 9,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,85</t>
+          <t>0,43; 4,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 6,45</t>
+          <t>1,05; 6,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,58; 10,65</t>
+          <t>4,56; 10,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,29; 9,9</t>
+          <t>3,06; 10,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,98; 5,59</t>
+          <t>1,01; 5,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 5,16</t>
+          <t>1,25; 5,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,66; 10,4</t>
+          <t>5,79; 10,11</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,93; 8,55</t>
+          <t>3,94; 8,45</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,75</t>
+          <t>0,94; 3,79</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 4,87</t>
+          <t>1,63; 4,62</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,02; 8,14</t>
+          <t>3,95; 8,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,48; 8,87</t>
+          <t>4,42; 8,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,6; 7,36</t>
+          <t>3,68; 7,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,89; 7,02</t>
+          <t>3,14; 6,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,28; 9,7</t>
+          <t>5,1; 9,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,14; 7,97</t>
+          <t>3,91; 8,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,45; 5,9</t>
+          <t>2,51; 5,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,04; 4,87</t>
+          <t>2,0; 4,93</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,13; 8,25</t>
+          <t>5,0; 7,94</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,65; 7,64</t>
+          <t>4,66; 7,54</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,47; 6,02</t>
+          <t>3,53; 5,98</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,88; 5,21</t>
+          <t>2,77; 5,19</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2799</t>
+          <t>0; 3156</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 3508</t>
+          <t>0; 3340</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>720; 6104</t>
+          <t>709; 6752</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3126; 12403</t>
+          <t>3248; 12049</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>662; 7092</t>
+          <t>1070; 7471</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1824; 7838</t>
+          <t>1659; 7888</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1359; 7529</t>
+          <t>1359; 7534</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2407; 10197</t>
+          <t>2334; 10548</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>754; 7772</t>
+          <t>745; 7675</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>621; 8050</t>
+          <t>665; 7563</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2788; 10623</t>
+          <t>2852; 10190</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6581; 19251</t>
+          <t>7305; 19281</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2575; 11235</t>
+          <t>2850; 11104</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3246; 12385</t>
+          <t>3462; 11950</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1905; 9135</t>
+          <t>1879; 9122</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3418; 11994</t>
+          <t>3553; 11535</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9130; 21560</t>
+          <t>9169; 21063</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4796; 14369</t>
+          <t>4662; 14414</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5571; 15948</t>
+          <t>5802; 15589</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3571; 11916</t>
+          <t>3513; 12760</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4165; 13848</t>
+          <t>4153; 13380</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2549; 11297</t>
+          <t>2441; 11351</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9394; 21566</t>
+          <t>9295; 21629</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8847; 21116</t>
+          <t>8836; 20733</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15420; 30955</t>
+          <t>15359; 30381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9218; 21842</t>
+          <t>9084; 21800</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8574; 20349</t>
+          <t>8703; 20090</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4522; 13753</t>
+          <t>4771; 14138</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>618; 5588</t>
+          <t>631; 6235</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2308; 12757</t>
+          <t>2067; 13041</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7962; 18507</t>
+          <t>7914; 18498</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4638; 13975</t>
+          <t>4317; 14603</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1331; 7600</t>
+          <t>1371; 7653</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2879; 12233</t>
+          <t>2970; 12408</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19097; 35072</t>
+          <t>19533; 34104</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11353; 24732</t>
+          <t>11391; 24423</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2701; 10537</t>
+          <t>2651; 10654</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6135; 21163</t>
+          <t>7092; 20094</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>14119; 28552</t>
+          <t>13855; 28870</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15861; 31414</t>
+          <t>15659; 31640</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13070; 26731</t>
+          <t>13357; 27656</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11319; 27500</t>
+          <t>12298; 27037</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>19093; 35073</t>
+          <t>18465; 34049</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15142; 29179</t>
+          <t>14294; 29573</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9018; 21743</t>
+          <t>9254; 21615</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9892; 23604</t>
+          <t>9669; 23862</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>36529; 58819</t>
+          <t>35600; 56580</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>33459; 55034</t>
+          <t>33571; 54266</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25371; 44038</t>
+          <t>25839; 43764</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>25192; 45601</t>
+          <t>24239; 45443</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP19C04-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP19C04-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -664,29 +664,29 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>12,08%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>13,3%</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -732,29 +732,29 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 51,33</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 59,37</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,05</t>
+          <t>0,0; 27,36</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4,29%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5,78%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3,89%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3,58%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>2,7%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>8,76%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>4,14%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6,08%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,29%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,78%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>3,89%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 8,01</t>
+          <t>1,69; 9,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,18; 15,51</t>
+          <t>2,25; 11,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,56; 10,88</t>
+          <t>1,04; 9,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,51; 11,92</t>
+          <t>0,78; 10,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,69; 9,37</t>
+          <t>0,42; 7,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,54; 11,46</t>
+          <t>4,49; 16,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 9,35</t>
+          <t>0,93; 9,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 9,81</t>
+          <t>2,83; 12,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,73; 6,18</t>
+          <t>1,68; 6,23</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,3; 11,36</t>
+          <t>4,26; 11,01</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,89; 7,36</t>
+          <t>1,81; 7,79</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,42; 8,34</t>
+          <t>2,31; 8,87</t>
         </is>
       </c>
     </row>
@@ -929,54 +929,54 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>9,39%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5,44%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5,22%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3,47%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>4,6%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>5,44%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>9,33%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7,11%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>9,39%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>7,26%</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>7,07%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>5,44%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5,22%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>7,07%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>5,44%</t>
-        </is>
-      </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
           <t>7,27%</t>
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,89; 9,2</t>
+          <t>5,32; 14,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,84; 9,22</t>
+          <t>2,66; 9,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,16; 14,14</t>
+          <t>2,71; 8,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,82; 11,82</t>
+          <t>1,46; 6,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,49; 14,75</t>
+          <t>1,99; 9,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,66; 9,66</t>
+          <t>2,7; 9,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,78; 8,96</t>
+          <t>5,7; 13,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,48; 6,89</t>
+          <t>3,6; 12,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,54; 10,56</t>
+          <t>4,82; 10,94</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,44; 8,06</t>
+          <t>3,36; 7,98</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,15; 10,19</t>
+          <t>5,03; 9,99</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,17; 7,6</t>
+          <t>3,04; 7,76</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7,04%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2,54%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>8,37%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>5,82%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1,69%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,88%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,04%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,32; 12,29</t>
+          <t>4,25; 10,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,23; 9,56</t>
+          <t>3,28; 10,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,3</t>
+          <t>0,99; 5,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 6,6</t>
+          <t>1,23; 5,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,56; 10,65</t>
+          <t>5,12; 12,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,06; 10,34</t>
+          <t>3,33; 9,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 5,63</t>
+          <t>0,43; 4,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 5,23</t>
+          <t>1,0; 4,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,79; 10,11</t>
+          <t>5,68; 10,18</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,94; 8,45</t>
+          <t>4,01; 8,42</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,79</t>
+          <t>0,95; 3,7</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,63; 4,62</t>
+          <t>1,39; 4,03</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>7,08%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5,73%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3,92%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>3,13%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>5,85%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>6,28%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>5,28%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,69%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>7,08%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,73%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,95; 8,23</t>
+          <t>5,24; 9,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,42; 8,94</t>
+          <t>3,98; 7,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,68; 7,61</t>
+          <t>2,4; 5,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,14; 6,9</t>
+          <t>1,93; 4,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,1; 9,41</t>
+          <t>4,11; 8,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,91; 8,08</t>
+          <t>4,5; 8,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,51; 5,86</t>
+          <t>3,59; 7,5</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,93</t>
+          <t>2,91; 6,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,0; 7,94</t>
+          <t>5,12; 8,06</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,66; 7,54</t>
+          <t>4,6; 7,69</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,53; 5,98</t>
+          <t>3,41; 6,05</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,77; 5,19</t>
+          <t>2,65; 5,01</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1524,27 +1524,27 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1592,29 +1592,29 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>565</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>707</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>565</t>
         </is>
       </c>
     </row>
@@ -1660,29 +1660,29 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>0; 2400</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3156</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 3340</t>
+          <t>0; 2941</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3454</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5320</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3196</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2418</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>2273</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>6807</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2839</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4022</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3454</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5320</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3196</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2751</t>
+          <t>3868</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6773</t>
+          <t>6286</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>709; 6752</t>
+          <t>1356; 7736</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3248; 12049</t>
+          <t>2072; 10378</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1070; 7471</t>
+          <t>851; 7699</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1659; 7888</t>
+          <t>524; 7031</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1359; 7534</t>
+          <t>355; 6388</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2334; 10548</t>
+          <t>3485; 12526</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>745; 7675</t>
+          <t>635; 6437</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>665; 7563</t>
+          <t>1796; 7874</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2852; 10190</t>
+          <t>2774; 10260</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7305; 19281</t>
+          <t>7224; 18695</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2850; 11104</t>
+          <t>2733; 11751</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3462; 11950</t>
+          <t>3021; 11616</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>9932</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>7181</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>7796</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5393</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>4559</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>6808</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>13887</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>8671</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>9932</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>7181</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>7796</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5727</t>
+          <t>8846</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14398</t>
+          <t>14239</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1879; 9122</t>
+          <t>5627; 15769</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3553; 11535</t>
+          <t>3516; 12696</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9169; 21063</t>
+          <t>4041; 13417</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4662; 14414</t>
+          <t>2275; 10616</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5802; 15589</t>
+          <t>1971; 9078</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3513; 12760</t>
+          <t>3377; 11356</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4153; 13380</t>
+          <t>8487; 20789</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2441; 11351</t>
+          <t>4391; 14684</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9295; 21629</t>
+          <t>9870; 22418</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8836; 20733</t>
+          <t>8651; 20535</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15359; 30381</t>
+          <t>15011; 29803</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9084; 21800</t>
+          <t>8415; 21497</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>12234</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>8478</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3453</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6057</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>13688</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>8605</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>2454</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5686</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>12234</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>8478</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3453</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6424</t>
+          <t>4510</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12109</t>
+          <t>10567</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8703; 20090</t>
+          <t>7385; 18350</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4771; 14138</t>
+          <t>4636; 14117</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>631; 6235</t>
+          <t>1348; 7005</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2067; 13041</t>
+          <t>2866; 12582</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7914; 18498</t>
+          <t>8377; 19982</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4317; 14603</t>
+          <t>4922; 14437</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1371; 7653</t>
+          <t>627; 6020</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2970; 12408</t>
+          <t>2040; 9113</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19533; 34104</t>
+          <t>19155; 34311</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11391; 24423</t>
+          <t>11593; 24336</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2651; 10654</t>
+          <t>2672; 10401</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7092; 20094</t>
+          <t>6079; 17652</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>26</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>25619</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>20978</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>14445</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>14433</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>20519</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>22220</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>19181</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>18379</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>25619</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>20978</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>14445</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15609</t>
+          <t>17224</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>33988</t>
+          <t>31657</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13855; 28870</t>
+          <t>18948; 34357</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15659; 31640</t>
+          <t>14563; 28916</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13357; 27656</t>
+          <t>8866; 22080</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12298; 27037</t>
+          <t>8914; 22960</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>18465; 34049</t>
+          <t>14407; 28733</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14294; 29573</t>
+          <t>15946; 31191</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9254; 21615</t>
+          <t>13055; 27246</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9669; 23862</t>
+          <t>11527; 25018</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>35600; 56580</t>
+          <t>36483; 57423</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>33571; 54266</t>
+          <t>33116; 55403</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25839; 43764</t>
+          <t>24962; 44272</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>24239; 45443</t>
+          <t>22739; 42952</t>
         </is>
       </c>
     </row>
